--- a/data-raw/metadata/lower_feather_metadata.xlsx
+++ b/data-raw/metadata/lower_feather_metadata.xlsx
@@ -1032,7 +1032,7 @@
         <v>44580</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46049</v>
+        <v>46066</v>
       </c>
     </row>
   </sheetData>

--- a/data-raw/metadata/lower_feather_metadata.xlsx
+++ b/data-raw/metadata/lower_feather_metadata.xlsx
@@ -1032,7 +1032,7 @@
         <v>44580</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46066</v>
+        <v>46049</v>
       </c>
     </row>
   </sheetData>

--- a/data-raw/metadata/lower_feather_metadata.xlsx
+++ b/data-raw/metadata/lower_feather_metadata.xlsx
@@ -1032,7 +1032,7 @@
         <v>44580</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46066</v>
+        <v>46113</v>
       </c>
     </row>
   </sheetData>

--- a/data-raw/metadata/lower_feather_metadata.xlsx
+++ b/data-raw/metadata/lower_feather_metadata.xlsx
@@ -1032,7 +1032,7 @@
         <v>44580</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46113</v>
+        <v>46134</v>
       </c>
     </row>
   </sheetData>

--- a/data-raw/metadata/lower_feather_metadata.xlsx
+++ b/data-raw/metadata/lower_feather_metadata.xlsx
@@ -1032,7 +1032,7 @@
         <v>44580</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46134</v>
+        <v>46154</v>
       </c>
     </row>
   </sheetData>
